--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618047.7692656383</v>
+        <v>618048</v>
       </c>
       <c r="R2" t="n">
-        <v>6692664.496591973</v>
+        <v>6692664</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2005-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98483</v>
+        <v>98489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98489</v>
+        <v>98492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98523</v>
+        <v>98529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98529</v>
+        <v>98536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28374-2025 artfynd.xlsx
+++ b/artfynd/A 28374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>93814333</v>
       </c>
       <c r="B2" t="n">
-        <v>98555</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
